--- a/outputs/56786.xlsx
+++ b/outputs/56786.xlsx
@@ -472,7 +472,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.22"/>
   </cols>
   <sheetData>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -483,17 +483,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
         <v>39843</v>
       </c>
       <c r="B4" s="4" t="n">
         <v>1.50000000139698</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="5" t="e">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A4-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A4))</f>
+        <v>#DIV/0!</v>
+      </c>
       <c r="D4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
         <v>39843</v>
       </c>
@@ -501,11 +504,12 @@
         <v>10.8333333337214</v>
       </c>
       <c r="C5" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A5-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A5))</f>
         <v>1.50000000139698</v>
       </c>
       <c r="D5" s="6"/>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
         <v>39850</v>
       </c>
@@ -513,11 +517,12 @@
         <v>27.9944444453577</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>6.16666666755918</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A6-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A6))</f>
+        <v>6.16666666755919</v>
       </c>
       <c r="D6" s="6"/>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
         <v>39850</v>
       </c>
@@ -525,11 +530,12 @@
         <v>2.16666666674428</v>
       </c>
       <c r="C7" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A7-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A7))</f>
         <v>13.442592593492</v>
       </c>
       <c r="D7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
         <v>39858</v>
       </c>
@@ -537,11 +543,12 @@
         <v>1877.06388888939</v>
       </c>
       <c r="C8" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A8-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A8))</f>
         <v>10.6236111118051</v>
       </c>
       <c r="D8" s="6"/>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="n">
         <v>39868</v>
       </c>
@@ -549,11 +556,12 @@
         <v>1282.61388888932</v>
       </c>
       <c r="C9" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A9-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A9))</f>
         <v>383.911666667322</v>
       </c>
       <c r="D9" s="6"/>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="n">
         <v>39881</v>
       </c>
@@ -561,11 +569,12 @@
         <v>2985.44166666688</v>
       </c>
       <c r="C10" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A10-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A10))</f>
         <v>533.695370370988</v>
       </c>
       <c r="D10" s="6"/>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
         <v>39903</v>
       </c>
@@ -573,11 +582,12 @@
         <v>3341.70277777885</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>883.944841270402</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A11-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A11))</f>
+        <v>883.944841270401</v>
       </c>
       <c r="D11" s="6"/>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="n">
         <v>39903</v>
       </c>
@@ -585,11 +595,12 @@
         <v>63.5000000009313</v>
       </c>
       <c r="C12" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A12-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A12))</f>
         <v>1191.16458333396</v>
       </c>
       <c r="D12" s="6"/>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
         <v>39906</v>
       </c>
@@ -597,11 +608,12 @@
         <v>559.083333332674</v>
       </c>
       <c r="C13" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A13-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A13))</f>
         <v>1065.86851851918</v>
       </c>
       <c r="D13" s="6"/>
     </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="n">
         <v>39906</v>
       </c>
@@ -609,11 +621,12 @@
         <v>0.0555555563187227</v>
       </c>
       <c r="C14" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A14-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A14))</f>
         <v>1015.19000000053</v>
       </c>
       <c r="D14" s="6"/>
     </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="n">
         <v>39907</v>
       </c>
@@ -621,11 +634,12 @@
         <v>171.27777777845</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>922.905050505598</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A15-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A15))</f>
+        <v>922.905050505599</v>
       </c>
       <c r="D15" s="6"/>
     </row>
-    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="n">
         <v>39907</v>
       </c>
@@ -633,11 +647,12 @@
         <v>4.3611111107748</v>
       </c>
       <c r="C16" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A16-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A16))</f>
         <v>860.269444445003</v>
       </c>
       <c r="D16" s="6"/>
     </row>
-    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="n">
         <v>39914</v>
       </c>
@@ -645,11 +660,12 @@
         <v>2.97222222201526</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>794.430341880831</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A17-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A17))</f>
+        <v>794.430341880832</v>
       </c>
       <c r="D17" s="6"/>
     </row>
-    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="n">
         <v>39914</v>
       </c>
@@ -657,11 +673,12 @@
         <v>28.0833333340706</v>
       </c>
       <c r="C18" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A18-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A18))</f>
         <v>737.897619048059</v>
       </c>
       <c r="D18" s="6"/>
     </row>
-    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="n">
         <v>39914</v>
       </c>
@@ -669,11 +686,12 @@
         <v>0.0833333336049691</v>
       </c>
       <c r="C19" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A19-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A19))</f>
         <v>690.576666667126</v>
       </c>
       <c r="D19" s="6"/>
     </row>
-    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="n">
         <v>39925</v>
       </c>
@@ -681,11 +699,12 @@
         <v>124.11111110996</v>
       </c>
       <c r="C20" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A20-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A20))</f>
         <v>647.420833333781</v>
       </c>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="n">
         <v>39932</v>
       </c>
@@ -693,11 +712,12 @@
         <v>1606.17777777719</v>
       </c>
       <c r="C21" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A21-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A21))</f>
         <v>616.637908497086</v>
       </c>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="n">
         <v>39932</v>
       </c>
@@ -705,11 +725,12 @@
         <v>2.02777777682059</v>
       </c>
       <c r="C22" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A22-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A22))</f>
         <v>671.612345679314</v>
       </c>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="n">
         <v>39934</v>
       </c>
@@ -717,11 +738,12 @@
         <v>399.419444444357</v>
       </c>
       <c r="C23" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A23-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A23))</f>
         <v>636.371052631814</v>
       </c>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="n">
         <v>39944</v>
       </c>
@@ -729,11 +751,12 @@
         <v>2514.38055555511</v>
       </c>
       <c r="C24" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A24-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A24))</f>
         <v>624.523472222441</v>
       </c>
       <c r="D24" s="6"/>
     </row>
-    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="n">
         <v>39945</v>
       </c>
@@ -741,11 +764,12 @@
         <v>173.838888889295</v>
       </c>
       <c r="C25" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A25-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A25))</f>
         <v>714.516666666854</v>
       </c>
       <c r="D25" s="6"/>
     </row>
-    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="n">
         <v>39948</v>
       </c>
@@ -753,11 +777,12 @@
         <v>419.977777777822</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>689.940404040601</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A26-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A26))</f>
+        <v>689.940404040602</v>
       </c>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="n">
         <v>39950</v>
       </c>
@@ -765,11 +790,12 @@
         <v>366.616666666232</v>
       </c>
       <c r="C27" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A27-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A27))</f>
         <v>678.202898550915</v>
       </c>
       <c r="D27" s="6"/>
     </row>
-    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="n">
         <v>39950</v>
       </c>
@@ -777,11 +803,12 @@
         <v>1.05277777765878</v>
       </c>
       <c r="C28" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A28-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A28))</f>
         <v>665.220138889054</v>
       </c>
       <c r="D28" s="6"/>
     </row>
-    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="n">
         <v>39958</v>
       </c>
@@ -789,11 +816,12 @@
         <v>0.138888889923692</v>
       </c>
       <c r="C29" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A29-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A29))</f>
         <v>638.653444444598</v>
       </c>
       <c r="D29" s="6"/>
     </row>
-    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="n">
         <v>39958</v>
       </c>
@@ -801,11 +829,12 @@
         <v>0.750000000698492</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>614.095192307879</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A30-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A30))</f>
+        <v>614.09519230788</v>
       </c>
       <c r="D30" s="6"/>
     </row>
-    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="n">
         <v>39988</v>
       </c>
@@ -813,11 +842,12 @@
         <v>2.49999999941792</v>
       </c>
       <c r="C31" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A31-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A31))</f>
         <v>591.37870370391</v>
       </c>
       <c r="D31" s="6"/>
     </row>
-    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="n">
         <v>39990</v>
       </c>
@@ -825,11 +855,12 @@
         <v>473.066666666418</v>
       </c>
       <c r="C32" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A32-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A32))</f>
         <v>570.347321428749</v>
       </c>
       <c r="D32" s="6"/>
     </row>
-    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="n">
         <v>39990</v>
       </c>
@@ -837,11 +868,12 @@
         <v>10.0833333347691</v>
       </c>
       <c r="C33" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A33-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A33))</f>
         <v>566.992816092117</v>
       </c>
       <c r="D33" s="6"/>
     </row>
-    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="n">
         <v>39991</v>
       </c>
@@ -849,11 +881,12 @@
         <v>195.222222221782</v>
       </c>
       <c r="C34" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A34-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A34))</f>
         <v>548.429166666872</v>
       </c>
       <c r="D34" s="6"/>
     </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="n">
         <v>39991</v>
       </c>
@@ -861,11 +894,12 @@
         <v>75.2777777781012</v>
       </c>
       <c r="C35" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A35-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A35))</f>
         <v>537.035394265418</v>
       </c>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="n">
         <v>39992</v>
       </c>
@@ -873,11 +907,12 @@
         <v>29.3888888892252</v>
       </c>
       <c r="C36" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A36-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A36))</f>
         <v>522.605468750189</v>
       </c>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="n">
         <v>39992</v>
       </c>
@@ -885,11 +920,12 @@
         <v>208.058333333465</v>
       </c>
       <c r="C37" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A37-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A37))</f>
         <v>507.659511784705</v>
       </c>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="n">
         <v>39993</v>
       </c>
@@ -897,11 +933,12 @@
         <v>104.086111112265</v>
       </c>
       <c r="C38" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A38-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A38))</f>
         <v>498.847712418492</v>
       </c>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="n">
         <v>39997</v>
       </c>
@@ -909,11 +946,12 @@
         <v>1094.06388889009</v>
       </c>
       <c r="C39" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A39-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A39))</f>
         <v>487.568809524029</v>
       </c>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="n">
         <v>40027</v>
       </c>
@@ -921,11 +959,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C40" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A40-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A40))</f>
         <v>504.415895061975</v>
       </c>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="n">
         <v>40028</v>
       </c>
@@ -933,11 +972,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C41" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A41-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A41))</f>
         <v>490.783108108366</v>
       </c>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="n">
         <v>40028</v>
       </c>
@@ -945,11 +985,12 @@
         <v>0.333333332673647</v>
       </c>
       <c r="C42" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A42-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A42))</f>
         <v>477.867836257578</v>
       </c>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="n">
         <v>40028</v>
       </c>
@@ -957,11 +998,12 @@
         <v>0.166666667209938</v>
       </c>
       <c r="C43" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A43-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A43))</f>
         <v>465.623361823606</v>
       </c>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="n">
         <v>40028</v>
       </c>
@@ -969,11 +1011,12 @@
         <v>0.666666667093523</v>
       </c>
       <c r="C44" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A44-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A44))</f>
         <v>453.986944444696</v>
       </c>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="n">
         <v>40028</v>
       </c>
@@ -981,11 +1024,12 @@
         <v>0.416666668024845</v>
       </c>
       <c r="C45" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A45-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A45))</f>
         <v>442.930352303779</v>
       </c>
       <c r="D45" s="6"/>
     </row>
-    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="n">
         <v>40028</v>
       </c>
@@ -993,11 +1037,12 @@
         <v>12.6944444450783</v>
       </c>
       <c r="C46" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A46-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A46))</f>
         <v>432.394312169594</v>
       </c>
       <c r="D46" s="6"/>
     </row>
-    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="n">
         <v>40028</v>
       </c>
@@ -1005,11 +1050,12 @@
         <v>3.05555555562023</v>
       </c>
       <c r="C47" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A47-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A47))</f>
         <v>422.633850129489</v>
       </c>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="n">
         <v>40062</v>
       </c>
@@ -1017,11 +1063,12 @@
         <v>2293.07222222211</v>
       </c>
       <c r="C48" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A48-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A48))</f>
         <v>413.097979798265</v>
       </c>
       <c r="D48" s="6"/>
     </row>
-    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="n">
         <v>40063</v>
       </c>
@@ -1029,11 +1076,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>454.875185185461</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A49-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A49))</f>
+        <v>454.875185185462</v>
       </c>
       <c r="D49" s="6"/>
     </row>
-    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="n">
         <v>40064</v>
       </c>
@@ -1041,11 +1089,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C50" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A50-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A50))</f>
         <v>444.986654589656</v>
       </c>
       <c r="D50" s="6"/>
     </row>
-    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="n">
         <v>40065</v>
       </c>
@@ -1053,11 +1102,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C51" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A51-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A51))</f>
         <v>435.518912529843</v>
       </c>
       <c r="D51" s="6"/>
     </row>
-    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="n">
         <v>40066</v>
       </c>
@@ -1065,11 +1115,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C52" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A52-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A52))</f>
         <v>426.445659722522</v>
       </c>
       <c r="D52" s="6"/>
     </row>
-    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="n">
         <v>40070</v>
       </c>
@@ -1077,11 +1128,12 @@
         <v>8.74999999883585</v>
       </c>
       <c r="C53" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A53-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A53))</f>
         <v>417.742743764479</v>
       </c>
       <c r="D53" s="6"/>
     </row>
-    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="n">
         <v>40070</v>
       </c>
@@ -1089,11 +1141,12 @@
         <v>0.0833333336049691</v>
       </c>
       <c r="C54" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A54-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A54))</f>
         <v>409.562888889166</v>
       </c>
       <c r="D54" s="6"/>
     </row>
-    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="n">
         <v>40078</v>
       </c>
@@ -1101,11 +1154,12 @@
         <v>1943.14444444492</v>
       </c>
       <c r="C55" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A55-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A55))</f>
         <v>401.53387799592</v>
       </c>
       <c r="D55" s="6"/>
     </row>
-    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="n">
         <v>40079</v>
       </c>
@@ -1113,11 +1167,12 @@
         <v>288.252777778544</v>
       </c>
       <c r="C56" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A56-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A56))</f>
         <v>431.180235043016</v>
       </c>
       <c r="D56" s="6"/>
     </row>
-    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="n">
         <v>40080</v>
       </c>
@@ -1125,11 +1180,12 @@
         <v>92.2222222213168</v>
       </c>
       <c r="C57" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A57-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A57))</f>
         <v>428.483490566328</v>
       </c>
       <c r="D57" s="6"/>
     </row>
-    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="n">
         <v>40080</v>
       </c>
@@ -1137,11 +1193,12 @@
         <v>0.0277777790324763</v>
       </c>
       <c r="C58" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A58-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A58))</f>
         <v>422.25643004142</v>
       </c>
       <c r="D58" s="6"/>
     </row>
-    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="n">
         <v>40080</v>
       </c>
@@ -1149,11 +1206,12 @@
         <v>0.0555555545724928</v>
       </c>
       <c r="C59" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A59-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A59))</f>
         <v>414.579545454831</v>
       </c>
       <c r="D59" s="6"/>
     </row>
-    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="n">
         <v>40080</v>
       </c>
@@ -1161,11 +1219,12 @@
         <v>0</v>
       </c>
       <c r="C60" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A60-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A60))</f>
         <v>407.17733134947</v>
       </c>
       <c r="D60" s="6"/>
     </row>
-    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="n">
         <v>40080</v>
       </c>
@@ -1173,11 +1232,12 @@
         <v>2.49999999941792</v>
       </c>
       <c r="C61" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A61-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A61))</f>
         <v>400.03386939597</v>
       </c>
       <c r="D61" s="6"/>
     </row>
-    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="n">
         <v>40086</v>
       </c>
@@ -1185,11 +1245,12 @@
         <v>1412.47500000056</v>
       </c>
       <c r="C62" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A62-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A62))</f>
         <v>393.179837164995</v>
       </c>
       <c r="D62" s="6"/>
     </row>
-    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="n">
         <v>40114</v>
       </c>
@@ -1197,11 +1258,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C63" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A63-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A63))</f>
         <v>410.456026365598</v>
       </c>
       <c r="D63" s="6"/>
     </row>
-    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="n">
         <v>40115</v>
       </c>
@@ -1209,11 +1271,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C64" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A64-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A64))</f>
         <v>403.615138889145</v>
       </c>
       <c r="D64" s="6"/>
     </row>
-    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="n">
         <v>40116</v>
       </c>
@@ -1221,11 +1284,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C65" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A65-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A65))</f>
         <v>396.998542805363</v>
       </c>
       <c r="D65" s="6"/>
     </row>
-    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="n">
         <v>40117</v>
       </c>
@@ -1233,11 +1297,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C66" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A66-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A66))</f>
         <v>390.595385304928</v>
       </c>
       <c r="D66" s="6"/>
     </row>
-    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="n">
         <v>40118</v>
       </c>
@@ -1245,11 +1310,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>384.395502645777</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A67-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A67))</f>
+        <v>384.395502645778</v>
       </c>
       <c r="D67" s="6"/>
     </row>
-    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="n">
         <v>40119</v>
       </c>
@@ -1257,11 +1323,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C68" s="5" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A68-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A68))</f>
         <v>378.389366319725</v>
       </c>
       <c r="D68" s="6"/>
     </row>
-    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="n">
         <v>40120</v>
       </c>
@@ -1269,11 +1336,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>372.56803418832</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A69-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A69))</f>
+        <v>372.568034188321</v>
       </c>
       <c r="D69" s="6"/>
     </row>
-    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="n">
         <v>40301</v>
       </c>
@@ -1281,11 +1349,12 @@
         <v>0.138888888177462</v>
       </c>
       <c r="C70" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A70-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A70))</f>
         <v>254.922946860227</v>
       </c>
       <c r="D70" s="6"/>
     </row>
-    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="n">
         <v>40302</v>
       </c>
@@ -1293,11 +1362,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C71" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A71-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A71))</f>
         <v>249.502009456566</v>
       </c>
       <c r="D71" s="6"/>
     </row>
-    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="n">
         <v>40302</v>
       </c>
@@ -1305,11 +1375,12 @@
         <v>59.6666666673264</v>
       </c>
       <c r="C72" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A72-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A72))</f>
         <v>244.304108796605</v>
       </c>
       <c r="D72" s="6"/>
     </row>
-    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="n">
         <v>40306</v>
       </c>
@@ -1317,11 +1388,12 @@
         <v>992.88888888841</v>
       </c>
       <c r="C73" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A73-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A73))</f>
         <v>240.535997732742</v>
       </c>
       <c r="D73" s="6"/>
     </row>
-    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="n">
         <v>40307</v>
       </c>
@@ -1329,11 +1401,12 @@
         <v>130.641666665906</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>255.583055555855</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A74-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A74))</f>
+        <v>255.583055555856</v>
       </c>
       <c r="D74" s="6"/>
     </row>
-    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="n">
         <v>40309</v>
       </c>
@@ -1341,11 +1414,12 @@
         <v>548.5277777788</v>
       </c>
       <c r="C75" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A75-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A75))</f>
         <v>253.133224401151</v>
       </c>
       <c r="D75" s="6"/>
     </row>
-    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="n">
         <v>40314</v>
       </c>
@@ -1353,11 +1427,12 @@
         <v>1090.6027777784</v>
       </c>
       <c r="C76" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A76-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A76))</f>
         <v>211.227040816638</v>
       </c>
       <c r="D76" s="6"/>
     </row>
-    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="n">
         <v>40320</v>
       </c>
@@ -1365,11 +1440,12 @@
         <v>1594.88055555616</v>
       </c>
       <c r="C77" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A77-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A77))</f>
         <v>230.68871527812</v>
       </c>
       <c r="D77" s="6"/>
     </row>
-    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="n">
         <v>40320</v>
       </c>
@@ -1377,11 +1453,12 @@
         <v>0.694444444379769</v>
       </c>
       <c r="C78" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A78-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A78))</f>
         <v>258.529365079713</v>
       </c>
       <c r="D78" s="6"/>
     </row>
-    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="n">
         <v>40323</v>
       </c>
@@ -1389,11 +1466,12 @@
         <v>573.613888888503</v>
       </c>
       <c r="C79" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A79-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A79))</f>
         <v>253.372666667006</v>
       </c>
       <c r="D79" s="6"/>
     </row>
-    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="n">
         <v>40323</v>
       </c>
@@ -1401,11 +1479,12 @@
         <v>0.666666667093523</v>
       </c>
       <c r="C80" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A80-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A80))</f>
         <v>259.651906318408</v>
       </c>
       <c r="D80" s="6"/>
     </row>
-    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="n">
         <v>40324</v>
       </c>
@@ -1413,11 +1492,12 @@
         <v>285.222222221782</v>
       </c>
       <c r="C81" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A81-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A81))</f>
         <v>264.840500000306</v>
       </c>
       <c r="D81" s="6"/>
     </row>
-    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="n">
         <v>40324</v>
       </c>
@@ -1425,11 +1505,12 @@
         <v>56.4416666660691</v>
       </c>
       <c r="C82" s="4" t="n">
-        <v>265.240141612491</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A82-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A82))</f>
+        <v>265.240141612492</v>
       </c>
       <c r="D82" s="6"/>
     </row>
-    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="n">
         <v>40325</v>
       </c>
@@ -1437,11 +1518,12 @@
         <v>76.4694444439374</v>
       </c>
       <c r="C83" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A83-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A83))</f>
         <v>261.22478632506</v>
       </c>
       <c r="D83" s="6"/>
     </row>
-    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="n">
         <v>40327</v>
       </c>
@@ -1449,11 +1531,12 @@
         <v>470.422222221969</v>
       </c>
       <c r="C84" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A84-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A84))</f>
         <v>257.738836478247</v>
       </c>
       <c r="D84" s="6"/>
     </row>
-    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="n">
         <v>40328</v>
       </c>
@@ -1461,11 +1544,12 @@
         <v>424.880555556156</v>
       </c>
       <c r="C85" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A85-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A85))</f>
         <v>261.677417695723</v>
       </c>
       <c r="D85" s="6"/>
     </row>
-    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="n">
         <v>40329</v>
       </c>
@@ -1473,11 +1557,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C86" s="4" t="n">
-        <v>264.644747475003</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A86-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A86))</f>
+        <v>264.644747475004</v>
       </c>
       <c r="D86" s="6"/>
     </row>
-    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="n">
         <v>40330</v>
       </c>
@@ -1485,11 +1570,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C87" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A87-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A87))</f>
         <v>259.918998016136</v>
       </c>
       <c r="D87" s="6"/>
     </row>
-    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="n">
         <v>40331</v>
       </c>
@@ -1497,11 +1583,12 @@
         <v>259.027777778101</v>
       </c>
       <c r="C88" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A88-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A88))</f>
         <v>255.359064327755</v>
       </c>
       <c r="D88" s="6"/>
     </row>
-    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="n">
         <v>40334</v>
       </c>
@@ -1509,11 +1596,12 @@
         <v>748.666666665813</v>
       </c>
       <c r="C89" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A89-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A89))</f>
         <v>255.422318007934</v>
       </c>
       <c r="D89" s="6"/>
     </row>
-    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="n">
         <v>40336</v>
       </c>
@@ -1521,11 +1609,12 @@
         <v>502.444444445428</v>
       </c>
       <c r="C90" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A90-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A90))</f>
         <v>263.782391713999</v>
       </c>
       <c r="D90" s="6"/>
     </row>
-    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="n">
         <v>40338</v>
       </c>
@@ -1533,11 +1622,12 @@
         <v>500.725000000675</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>267.760092592856</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A91-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A91))</f>
+        <v>267.760092592857</v>
       </c>
       <c r="D91" s="6"/>
     </row>
-    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="n">
         <v>40343</v>
       </c>
@@ -1545,11 +1635,12 @@
         <v>1187.56111111085</v>
       </c>
       <c r="C92" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A92-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A92))</f>
         <v>271.579189435608</v>
       </c>
       <c r="D92" s="6"/>
     </row>
-    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="n">
         <v>40344</v>
       </c>
@@ -1557,11 +1648,12 @@
         <v>149.194444444729</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>286.353091398111</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A93-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A93))</f>
+        <v>286.353091398112</v>
       </c>
       <c r="D93" s="6"/>
     </row>
-    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="n">
         <v>40348</v>
       </c>
@@ -1569,11 +1661,12 @@
         <v>1094.1333333333</v>
       </c>
       <c r="C94" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A94-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A94))</f>
         <v>284.175970017899</v>
       </c>
       <c r="D94" s="6"/>
     </row>
-    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="n">
         <v>40349</v>
       </c>
@@ -1581,11 +1674,12 @@
         <v>172.419444444822</v>
       </c>
       <c r="C95" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A95-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A95))</f>
         <v>296.831553819702</v>
       </c>
       <c r="D95" s="6"/>
     </row>
-    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="n">
         <v>40355</v>
       </c>
@@ -1593,11 +1687,12 @@
         <v>1339.97499999998</v>
       </c>
       <c r="C96" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A96-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A96))</f>
         <v>299.486545139162</v>
       </c>
       <c r="D96" s="6"/>
     </row>
-    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="n">
         <v>40355</v>
       </c>
@@ -1605,11 +1700,12 @@
         <v>37.4444444436813</v>
       </c>
       <c r="C97" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A97-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A97))</f>
         <v>315.494059829328</v>
       </c>
       <c r="D97" s="6"/>
     </row>
-    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="n">
         <v>40363</v>
       </c>
@@ -1617,11 +1713,12 @@
         <v>1757.70277777745</v>
       </c>
       <c r="C98" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A98-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A98))</f>
         <v>316.470881226274</v>
       </c>
       <c r="D98" s="6"/>
     </row>
-    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="n">
         <v>40364</v>
       </c>
@@ -1629,11 +1726,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C99" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A99-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A99))</f>
         <v>340.898540489853</v>
       </c>
       <c r="D99" s="6"/>
     </row>
-    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="n">
         <v>40369</v>
       </c>
@@ -1641,11 +1739,12 @@
         <v>1232.25277777703</v>
       </c>
       <c r="C100" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A100-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A100))</f>
         <v>335.216944444663</v>
       </c>
       <c r="D100" s="6"/>
     </row>
-    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="n">
         <v>40369</v>
       </c>
@@ -1653,11 +1752,12 @@
         <v>63.6944444454275</v>
       </c>
       <c r="C101" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A101-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A101))</f>
         <v>349.922449909128</v>
       </c>
       <c r="D101" s="6"/>
     </row>
-    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="n">
         <v>40370</v>
       </c>
@@ -1665,11 +1765,12 @@
         <v>186.883333334117</v>
       </c>
       <c r="C102" s="4" t="n">
-        <v>345.305869175842</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A102-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A102))</f>
+        <v>345.305869175843</v>
       </c>
       <c r="D102" s="6"/>
     </row>
-    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="n">
         <v>40371</v>
       </c>
@@ -1677,11 +1778,12 @@
         <v>212.391666666954</v>
       </c>
       <c r="C103" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A103-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A103))</f>
         <v>342.791225749783</v>
       </c>
       <c r="D103" s="6"/>
     </row>
-    <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="n">
         <v>40371</v>
       </c>
@@ -1689,11 +1791,12 @@
         <v>7.55555555457249</v>
       </c>
       <c r="C104" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A104-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A104))</f>
         <v>340.753732639114</v>
       </c>
       <c r="D104" s="6"/>
     </row>
-    <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="n">
         <v>40371</v>
       </c>
@@ -1701,11 +1804,12 @@
         <v>20.8611111121718</v>
       </c>
       <c r="C105" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A105-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A105))</f>
         <v>335.627606837813</v>
       </c>
       <c r="D105" s="6"/>
     </row>
-    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="n">
         <v>40372</v>
       </c>
@@ -1713,11 +1817,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C106" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A106-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A106))</f>
         <v>330.858417508637</v>
       </c>
       <c r="D106" s="6"/>
     </row>
-    <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="n">
         <v>40375</v>
       </c>
@@ -1725,11 +1830,12 @@
         <v>827.341666665743</v>
       </c>
       <c r="C107" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A107-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A107))</f>
         <v>325.920273632067</v>
       </c>
       <c r="D107" s="6"/>
     </row>
-    <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="n">
         <v>40377</v>
       </c>
@@ -1737,11 +1843,12 @@
         <v>378.663888889714</v>
       </c>
       <c r="C108" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A108-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A108))</f>
         <v>333.294117647268</v>
       </c>
       <c r="D108" s="6"/>
     </row>
-    <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="n">
         <v>40379</v>
       </c>
@@ -1749,11 +1856,12 @@
         <v>472.225000000326</v>
       </c>
       <c r="C109" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A109-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A109))</f>
         <v>333.951650563825</v>
       </c>
       <c r="D109" s="6"/>
     </row>
-    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="n">
         <v>40380</v>
       </c>
@@ -1761,11 +1869,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C110" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A110-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A110))</f>
         <v>335.926984127204</v>
       </c>
       <c r="D110" s="6"/>
     </row>
-    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="n">
         <v>40381</v>
       </c>
@@ -1773,11 +1882,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C111" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A111-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A111))</f>
         <v>331.195657277221</v>
       </c>
       <c r="D111" s="6"/>
     </row>
-    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="n">
         <v>40383</v>
       </c>
@@ -1785,11 +1895,12 @@
         <v>522.724999999045</v>
       </c>
       <c r="C112" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A112-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A112))</f>
         <v>326.595756173071</v>
       </c>
       <c r="D112" s="6"/>
     </row>
-    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="n">
         <v>40388</v>
       </c>
@@ -1797,11 +1908,12 @@
         <v>1256.28055555571</v>
       </c>
       <c r="C113" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A113-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A113))</f>
         <v>329.28245814329</v>
       </c>
       <c r="D113" s="6"/>
     </row>
-    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="n">
         <v>40389</v>
       </c>
@@ -1809,11 +1921,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C114" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A114-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A114))</f>
         <v>341.809459459674</v>
       </c>
       <c r="D114" s="6"/>
     </row>
-    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="n">
         <v>40390</v>
       </c>
@@ -1821,11 +1934,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C115" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A115-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A115))</f>
         <v>337.252037037257</v>
       </c>
       <c r="D115" s="6"/>
     </row>
-    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="n">
         <v>40391</v>
       </c>
@@ -1833,11 +1947,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C116" s="4" t="n">
-        <v>332.814546783851</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A116-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A116))</f>
+        <v>332.814546783852</v>
       </c>
       <c r="D116" s="6"/>
     </row>
-    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="n">
         <v>40406</v>
       </c>
@@ -1845,11 +1960,12 @@
         <v>0.333333334419876</v>
       </c>
       <c r="C117" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A117-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A117))</f>
         <v>366.327093397951</v>
       </c>
       <c r="D117" s="6"/>
     </row>
-    <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="n">
         <v>40410</v>
       </c>
@@ -1857,11 +1973,12 @@
         <v>907.116666666116</v>
       </c>
       <c r="C118" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A118-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A118))</f>
         <v>361.098611111329</v>
       </c>
       <c r="D118" s="6"/>
     </row>
-    <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="n">
         <v>40411</v>
       </c>
@@ -1869,11 +1986,12 @@
         <v>284.222222222015</v>
       </c>
       <c r="C119" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A119-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A119))</f>
         <v>368.789006259988</v>
       </c>
       <c r="D119" s="6"/>
     </row>
-    <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="n">
         <v>40412</v>
       </c>
@@ -1881,11 +1999,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C120" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A120-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A120))</f>
         <v>367.614467592794</v>
       </c>
       <c r="D120" s="6"/>
     </row>
-    <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="n">
         <v>40413</v>
       </c>
@@ -1893,11 +2012,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C121" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A121-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A121))</f>
         <v>362.578691019994</v>
       </c>
       <c r="D121" s="6"/>
     </row>
-    <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="n">
         <v>40414</v>
       </c>
@@ -1905,11 +2025,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C122" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A122-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A122))</f>
         <v>357.67901651673</v>
       </c>
       <c r="D122" s="6"/>
     </row>
-    <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="n">
         <v>40415</v>
       </c>
@@ -1917,11 +2038,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C123" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A123-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A123))</f>
         <v>352.910000000219</v>
       </c>
       <c r="D123" s="6"/>
     </row>
-    <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="n">
         <v>40416</v>
       </c>
@@ -1929,11 +2051,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C124" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A124-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A124))</f>
         <v>348.266483918353</v>
       </c>
       <c r="D124" s="6"/>
     </row>
-    <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="n">
         <v>40417</v>
       </c>
@@ -1941,11 +2064,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C125" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A125-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A125))</f>
         <v>343.743578643809</v>
       </c>
       <c r="D125" s="6"/>
     </row>
-    <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="n">
         <v>40418</v>
       </c>
@@ -1953,11 +2077,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C126" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A126-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A126))</f>
         <v>339.336645299381</v>
       </c>
       <c r="D126" s="6"/>
     </row>
-    <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="n">
         <v>40426</v>
       </c>
@@ -1965,11 +2090,12 @@
         <v>2146.56666666793</v>
       </c>
       <c r="C127" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A127-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A127))</f>
         <v>335.041279887723</v>
       </c>
       <c r="D127" s="6"/>
     </row>
-    <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="n">
         <v>40427</v>
       </c>
@@ -1977,11 +2103,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C128" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A128-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A128))</f>
         <v>357.685347222476</v>
       </c>
       <c r="D128" s="6"/>
     </row>
-    <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="n">
         <v>40428</v>
       </c>
@@ -1989,11 +2116,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C129" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A129-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A129))</f>
         <v>329.02197916693</v>
       </c>
       <c r="D129" s="6"/>
     </row>
-    <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="n">
         <v>40428</v>
       </c>
@@ -2001,11 +2129,12 @@
         <v>0.833333334303461</v>
       </c>
       <c r="C130" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A130-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A130))</f>
         <v>324.960013717689</v>
       </c>
       <c r="D130" s="6"/>
     </row>
-    <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="n">
         <v>40438</v>
       </c>
@@ -2013,11 +2142,12 @@
         <v>2444.14722222195</v>
       </c>
       <c r="C131" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A131-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A131))</f>
         <v>346.233552631855</v>
       </c>
       <c r="D131" s="6"/>
     </row>
-    <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="n">
         <v>40444</v>
       </c>
@@ -2025,11 +2155,12 @@
         <v>1392.09166666784</v>
       </c>
       <c r="C132" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A132-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A132))</f>
         <v>352.82569444471</v>
       </c>
       <c r="D132" s="6"/>
     </row>
-    <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="n">
         <v>40451</v>
       </c>
@@ -2037,11 +2168,12 @@
         <v>1539.94999999995</v>
       </c>
       <c r="C133" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A133-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A133))</f>
         <v>391.884311424408</v>
       </c>
       <c r="D133" s="6"/>
     </row>
-    <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="n">
         <v>40451</v>
       </c>
@@ -2049,11 +2181,12 @@
         <v>0.666666667093523</v>
       </c>
       <c r="C134" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A134-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A134))</f>
         <v>407.829668210179</v>
       </c>
       <c r="D134" s="6"/>
     </row>
-    <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="n">
         <v>40455</v>
       </c>
@@ -2061,11 +2194,12 @@
         <v>1015.58333333291</v>
       </c>
       <c r="C135" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A135-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A135))</f>
         <v>388.221219136103</v>
       </c>
       <c r="D135" s="6"/>
     </row>
-    <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="n">
         <v>40464</v>
       </c>
@@ -2073,11 +2207,12 @@
         <v>2114.90000000107</v>
       </c>
       <c r="C136" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A136-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A136))</f>
         <v>396.815220700443</v>
       </c>
       <c r="D136" s="6"/>
     </row>
-    <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="n">
         <v>40470</v>
       </c>
@@ -2085,11 +2220,12 @@
         <v>1353.75555555511</v>
       </c>
       <c r="C137" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A137-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A137))</f>
         <v>420.032582582884</v>
       </c>
       <c r="D137" s="6"/>
     </row>
-    <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="n">
         <v>40471</v>
       </c>
@@ -2097,11 +2233,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C138" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A138-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A138))</f>
         <v>432.482222222514</v>
       </c>
       <c r="D138" s="6"/>
     </row>
-    <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="n">
         <v>40471</v>
       </c>
@@ -2109,11 +2246,12 @@
         <v>5.24999999965075</v>
       </c>
       <c r="C139" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A139-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A139))</f>
         <v>426.79170321667</v>
       </c>
       <c r="D139" s="6"/>
     </row>
-    <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="n">
         <v>40474</v>
       </c>
@@ -2121,11 +2259,12 @@
         <v>728.002777778311</v>
       </c>
       <c r="C140" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A140-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A140))</f>
         <v>421.317135642423</v>
       </c>
       <c r="D140" s="6"/>
     </row>
-    <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="n">
         <v>40475</v>
       </c>
@@ -2133,11 +2272,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C141" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A141-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A141))</f>
         <v>425.249002849294</v>
       </c>
       <c r="D141" s="6"/>
     </row>
-    <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="n">
         <v>40483</v>
       </c>
@@ -2145,11 +2285,12 @@
         <v>1924.85000000044</v>
       </c>
       <c r="C142" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A142-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A142))</f>
         <v>442.258851852128</v>
       </c>
       <c r="D142" s="6"/>
     </row>
-    <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="n">
         <v>40486</v>
       </c>
@@ -2157,11 +2298,12 @@
         <v>841.89166666707</v>
       </c>
       <c r="C143" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A143-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A143))</f>
         <v>480.743226788696</v>
       </c>
       <c r="D143" s="6"/>
     </row>
-    <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="n">
         <v>40487</v>
       </c>
@@ -2169,11 +2311,12 @@
         <v>163.333333333139</v>
       </c>
       <c r="C144" s="4" t="n">
-        <v>485.623611111376</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A144-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A144))</f>
+        <v>485.623611111377</v>
       </c>
       <c r="D144" s="6"/>
     </row>
-    <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="n">
         <v>40487</v>
       </c>
@@ -2181,11 +2324,12 @@
         <v>0.194444444496185</v>
       </c>
       <c r="C145" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A145-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A145))</f>
         <v>481.326407407667</v>
       </c>
       <c r="D145" s="6"/>
     </row>
-    <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="n">
         <v>40492</v>
       </c>
@@ -2193,11 +2337,12 @@
         <v>1263.00833333284</v>
       </c>
       <c r="C146" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A146-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A146))</f>
         <v>474.995723684467</v>
       </c>
       <c r="D146" s="6"/>
     </row>
-    <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="n">
         <v>40495</v>
       </c>
@@ -2205,11 +2350,12 @@
         <v>787.472222222714</v>
       </c>
       <c r="C147" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A147-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A147))</f>
         <v>485.2296536799</v>
       </c>
       <c r="D147" s="6"/>
     </row>
-    <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="n">
         <v>40498</v>
       </c>
@@ -2217,11 +2363,12 @@
         <v>591.755555556156</v>
       </c>
       <c r="C148" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A148-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A148))</f>
         <v>489.104558404808</v>
       </c>
       <c r="D148" s="6"/>
     </row>
-    <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="n">
         <v>40498</v>
       </c>
@@ -2229,11 +2376,12 @@
         <v>70.9472222230397</v>
       </c>
       <c r="C149" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A149-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A149))</f>
         <v>490.403938115585</v>
       </c>
       <c r="D149" s="6"/>
     </row>
-    <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="n">
         <v>40498</v>
       </c>
@@ -2241,11 +2389,12 @@
         <v>1.27777777786832</v>
       </c>
       <c r="C150" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A150-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A150))</f>
         <v>485.160729166928</v>
       </c>
       <c r="D150" s="6"/>
     </row>
-    <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="n">
         <v>40498</v>
       </c>
@@ -2253,11 +2402,12 @@
         <v>1.49999999965075</v>
       </c>
       <c r="C151" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A151-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A151))</f>
         <v>479.186865569532</v>
       </c>
       <c r="D151" s="6"/>
     </row>
-    <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="n">
         <v>40502</v>
       </c>
@@ -2265,11 +2415,12 @@
         <v>806.311111109681</v>
       </c>
       <c r="C152" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A152-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A152))</f>
         <v>473.361415989412</v>
       </c>
       <c r="D152" s="6"/>
     </row>
-    <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="n">
         <v>40503</v>
       </c>
@@ -2277,11 +2428,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>477.372858099294</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A153-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A153))</f>
+        <v>477.372858099295</v>
       </c>
       <c r="D153" s="6"/>
     </row>
-    <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="n">
         <v>40504</v>
       </c>
@@ -2289,11 +2441,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C154" s="4" t="n">
-        <v>471.689880952617</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A154-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A154))</f>
+        <v>471.689880952618</v>
       </c>
       <c r="D154" s="6"/>
     </row>
-    <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="n">
         <v>40505</v>
       </c>
@@ -2301,11 +2454,12 @@
         <v>116.041666666861</v>
       </c>
       <c r="C155" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A155-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A155))</f>
         <v>466.140620915274</v>
       </c>
       <c r="D155" s="6"/>
     </row>
-    <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="n">
         <v>40506</v>
       </c>
@@ -2313,11 +2467,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C156" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A156-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A156))</f>
         <v>462.069702842618</v>
       </c>
       <c r="D156" s="6"/>
     </row>
-    <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="n">
         <v>40507</v>
       </c>
@@ -2325,11 +2480,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C157" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A157-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A157))</f>
         <v>456.75858876142</v>
       </c>
       <c r="D157" s="6"/>
     </row>
-    <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="n">
         <v>40508</v>
       </c>
@@ -2337,11 +2493,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C158" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A158-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A158))</f>
         <v>451.568181818432</v>
       </c>
       <c r="D158" s="6"/>
     </row>
-    <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="n">
         <v>40509</v>
       </c>
@@ -2349,11 +2506,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C159" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A159-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A159))</f>
         <v>446.494413233713</v>
       </c>
       <c r="D159" s="6"/>
     </row>
-    <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="n">
         <v>40509</v>
       </c>
@@ -2361,11 +2519,12 @@
         <v>22.7777777781012</v>
       </c>
       <c r="C160" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A160-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A160))</f>
         <v>441.533395061987</v>
       </c>
       <c r="D160" s="6"/>
     </row>
-    <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="n">
         <v>40512</v>
       </c>
@@ -2373,11 +2532,12 @@
         <v>726.00277777703</v>
       </c>
       <c r="C161" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A161-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A161))</f>
         <v>436.931684981945</v>
       </c>
       <c r="D161" s="6"/>
     </row>
-    <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="n">
         <v>40512</v>
       </c>
@@ -2385,11 +2545,12 @@
         <v>27.502777777263</v>
       </c>
       <c r="C162" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A162-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A162))</f>
         <v>440.073762077543</v>
       </c>
       <c r="D162" s="6"/>
     </row>
-    <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="n">
         <v>40546</v>
       </c>
@@ -2397,11 +2558,12 @@
         <v>346.030555555481</v>
       </c>
       <c r="C163" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A163-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A163))</f>
         <v>435.63751493453</v>
       </c>
       <c r="D163" s="6"/>
     </row>
-    <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="n">
         <v>40548</v>
       </c>
@@ -2409,11 +2571,12 @@
         <v>401.830555555061</v>
       </c>
       <c r="C164" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A164-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A164))</f>
         <v>434.684249409221</v>
       </c>
       <c r="D164" s="6"/>
     </row>
-    <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="n">
         <v>40551</v>
       </c>
@@ -2421,11 +2584,12 @@
         <v>712.391666667536</v>
       </c>
       <c r="C165" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A165-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A165))</f>
         <v>434.338421052861</v>
       </c>
       <c r="D165" s="6"/>
     </row>
-    <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="n">
         <v>40551</v>
       </c>
@@ -2433,11 +2597,12 @@
         <v>5.99999999860302</v>
       </c>
       <c r="C166" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A166-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A166))</f>
         <v>437.234809028014</v>
       </c>
       <c r="D166" s="6"/>
     </row>
-    <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="n">
         <v>40551</v>
       </c>
@@ -2445,11 +2610,12 @@
         <v>2.91666666744277</v>
       </c>
       <c r="C167" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A167-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A167))</f>
         <v>432.789089347298</v>
       </c>
       <c r="D167" s="6"/>
     </row>
-    <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="n">
         <v>40551</v>
       </c>
@@ -2457,11 +2623,12 @@
         <v>0.0833333336049691</v>
       </c>
       <c r="C168" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A168-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A168))</f>
         <v>428.402636054647</v>
       </c>
       <c r="D168" s="6"/>
     </row>
-    <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="n">
         <v>40557</v>
       </c>
@@ -2469,11 +2636,12 @@
         <v>1355.25555555651</v>
       </c>
       <c r="C169" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A169-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A169))</f>
         <v>424.076178451404</v>
       </c>
       <c r="D169" s="6"/>
     </row>
-    <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="n">
         <v>40557</v>
       </c>
@@ -2481,11 +2649,12 @@
         <v>5.08333333244082</v>
       </c>
       <c r="C170" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A170-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A170))</f>
         <v>433.387972222455</v>
       </c>
       <c r="D170" s="6"/>
     </row>
-    <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="n">
         <v>40562</v>
       </c>
@@ -2493,11 +2662,12 @@
         <v>1086.19722222153</v>
       </c>
       <c r="C171" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A171-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A171))</f>
         <v>429.147332233445</v>
       </c>
       <c r="D171" s="6"/>
     </row>
-    <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="n">
         <v>40573</v>
       </c>
@@ -2505,11 +2675,12 @@
         <v>2755.41111111059</v>
       </c>
       <c r="C172" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A172-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A172))</f>
         <v>435.588997821563</v>
       </c>
       <c r="D172" s="6"/>
     </row>
-    <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="n">
         <v>40574</v>
       </c>
@@ -2517,11 +2688,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C173" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A173-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A173))</f>
         <v>458.111542610777</v>
       </c>
       <c r="D173" s="6"/>
     </row>
-    <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="n">
         <v>40575</v>
       </c>
@@ -2529,11 +2701,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C174" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A174-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A174))</f>
         <v>453.706650641235</v>
       </c>
       <c r="D174" s="6"/>
     </row>
-    <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="n">
         <v>40576</v>
       </c>
@@ -2541,11 +2714,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C175" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A175-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A175))</f>
         <v>449.385661375875</v>
       </c>
       <c r="D175" s="6"/>
     </row>
-    <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="n">
         <v>40577</v>
       </c>
@@ -2553,11 +2727,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C176" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A176-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A176))</f>
         <v>445.146200209862</v>
       </c>
       <c r="D176" s="6"/>
     </row>
-    <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="n">
         <v>40578</v>
       </c>
@@ -2565,11 +2740,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C177" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A177-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A177))</f>
         <v>440.985981308633</v>
       </c>
       <c r="D177" s="6"/>
     </row>
-    <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="n">
         <v>40579</v>
       </c>
@@ -2577,11 +2753,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>436.902803498168</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A178-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A178))</f>
+        <v>436.902803498169</v>
       </c>
       <c r="D178" s="6"/>
     </row>
-    <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="n">
         <v>40579</v>
       </c>
@@ -2589,11 +2766,12 @@
         <v>5.11111111147329</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>432.894546381473</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A179-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A179))</f>
+        <v>432.894546381474</v>
       </c>
       <c r="D179" s="6"/>
     </row>
-    <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="n">
         <v>40584</v>
       </c>
@@ -2601,11 +2779,12 @@
         <v>1277.58611111145</v>
       </c>
       <c r="C180" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A180-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A180))</f>
         <v>429.005606060837</v>
       </c>
       <c r="D180" s="6"/>
     </row>
-    <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="n">
         <v>40585</v>
       </c>
@@ -2613,11 +2792,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>436.650475475707</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A181-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A181))</f>
+        <v>436.650475475708</v>
       </c>
       <c r="D181" s="6"/>
     </row>
-    <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="n">
         <v>40585</v>
       </c>
@@ -2625,11 +2805,12 @@
         <v>19.2499999998836</v>
       </c>
       <c r="C182" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A182-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A182))</f>
         <v>432.751835317696</v>
       </c>
       <c r="D182" s="6"/>
     </row>
-    <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="n">
         <v>40586</v>
       </c>
@@ -2637,11 +2818,12 @@
         <v>300.277777778101</v>
       </c>
       <c r="C183" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A183-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A183))</f>
         <v>429.092527040547</v>
       </c>
       <c r="D183" s="6"/>
     </row>
-    <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="n">
         <v>40590</v>
       </c>
@@ -2649,11 +2831,12 @@
         <v>787.199999999721</v>
       </c>
       <c r="C184" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A184-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A184))</f>
         <v>427.962573099649</v>
       </c>
       <c r="D184" s="6"/>
     </row>
-    <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="n">
         <v>40590</v>
       </c>
@@ -2661,11 +2844,12 @@
         <v>0.222222221782431</v>
       </c>
       <c r="C185" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A185-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A185))</f>
         <v>431.086376811823</v>
       </c>
       <c r="D185" s="6"/>
     </row>
-    <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="n">
         <v>40593</v>
       </c>
@@ -2673,11 +2857,12 @@
         <v>840.727777776774</v>
       </c>
       <c r="C186" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A186-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A186))</f>
         <v>427.372030651564</v>
       </c>
       <c r="D186" s="6"/>
     </row>
-    <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="n">
         <v>40596</v>
       </c>
@@ -2685,11 +2870,12 @@
         <v>669.997222222737</v>
       </c>
       <c r="C187" s="4" t="n">
-        <v>430.904985755198</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A187-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A187))</f>
+        <v>430.904985755199</v>
       </c>
       <c r="D187" s="6"/>
     </row>
-    <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="n">
         <v>40695</v>
       </c>
@@ -2697,11 +2883,12 @@
         <v>3057.41388888855</v>
       </c>
       <c r="C188" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A188-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A188))</f>
         <v>443.367491749416</v>
       </c>
       <c r="D188" s="6"/>
     </row>
-    <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="n">
         <v>40702</v>
       </c>
@@ -2709,11 +2896,12 @@
         <v>1660.14444444445</v>
       </c>
       <c r="C189" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A189-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A189))</f>
         <v>472.728458050121</v>
       </c>
       <c r="D189" s="6"/>
     </row>
-    <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="n">
         <v>40706</v>
       </c>
@@ -2721,11 +2909,12 @@
         <v>874.169444444706</v>
       </c>
       <c r="C190" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A190-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A190))</f>
         <v>484.55926870771</v>
       </c>
       <c r="D190" s="6"/>
     </row>
-    <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="n">
         <v>40707</v>
       </c>
@@ -2733,11 +2922,12 @@
         <v>255.780555554666</v>
       </c>
       <c r="C191" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A191-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A191))</f>
         <v>488.494725028286</v>
       </c>
       <c r="D191" s="6"/>
     </row>
-    <row r="192" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="n">
         <v>40707</v>
       </c>
@@ -2745,11 +2935,12 @@
         <v>0.0277777772862464</v>
       </c>
       <c r="C192" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A192-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A192))</f>
         <v>486.16758333355</v>
       </c>
       <c r="D192" s="6"/>
     </row>
-    <row r="193" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="n">
         <v>40707</v>
       </c>
@@ -2757,11 +2948,12 @@
         <v>0.666666665347293</v>
       </c>
       <c r="C193" s="4" t="n">
-        <v>481.354317932002</v>
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A193-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A193))</f>
+        <v>481.354317932003</v>
       </c>
       <c r="D193" s="6"/>
     </row>
-    <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="n">
         <v>40710</v>
       </c>
@@ -2769,11 +2961,12 @@
         <v>687.891666666255</v>
       </c>
       <c r="C194" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A194-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A194))</f>
         <v>472.80697222242</v>
       </c>
       <c r="D194" s="6"/>
     </row>
-    <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="n">
         <v>40711</v>
       </c>
@@ -2781,11 +2974,12 @@
         <v>289.580555555876</v>
       </c>
       <c r="C195" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A195-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A195))</f>
         <v>474.936523652557</v>
       </c>
       <c r="D195" s="6"/>
     </row>
-    <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="n">
         <v>40716</v>
       </c>
@@ -2793,11 +2987,12 @@
         <v>1074.41944444436</v>
       </c>
       <c r="C196" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A196-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A196))</f>
         <v>469.91616666686</v>
       </c>
       <c r="D196" s="6"/>
     </row>
-    <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="n">
         <v>40717</v>
       </c>
@@ -2805,11 +3000,12 @@
         <v>0.00277777842711657</v>
       </c>
       <c r="C197" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A197-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A197))</f>
         <v>475.901347634954</v>
       </c>
       <c r="D197" s="6"/>
     </row>
-    <row r="198" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="n">
         <v>40720</v>
       </c>
@@ -2817,11 +3013,12 @@
         <v>746.344444443821</v>
       </c>
       <c r="C198" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A198-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A198))</f>
         <v>471.235675381459</v>
       </c>
       <c r="D198" s="6"/>
     </row>
-    <row r="199" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="n">
         <v>40720</v>
       </c>
@@ -2829,11 +3026,12 @@
         <v>0.0277777772862464</v>
       </c>
       <c r="C199" s="4" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A199-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A199))</f>
         <v>473.906634304395</v>
       </c>
       <c r="D199" s="6"/>
     </row>
-    <row r="200" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="7" t="n">
         <v>40720</v>
       </c>
@@ -2841,953 +3039,954 @@
         <v>9.53055555699393</v>
       </c>
       <c r="C200" s="8" t="n">
+        <f aca="false">AVERAGEIFS(B$4:B$200,A$4:A$200,"&gt;="&amp;A200-365,ROW(A$4:A$200),"&lt;"&amp;ROW(A200))</f>
         <v>469.350106837788</v>
       </c>
       <c r="D200" s="6"/>
     </row>
-    <row r="201" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D201" s="6"/>
     </row>
-    <row r="202" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D202" s="6"/>
     </row>
-    <row r="203" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D203" s="6"/>
     </row>
-    <row r="204" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D204" s="6"/>
     </row>
-    <row r="205" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D205" s="6"/>
     </row>
-    <row r="206" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D206" s="6"/>
     </row>
-    <row r="207" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D207" s="6"/>
     </row>
-    <row r="208" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D208" s="6"/>
     </row>
-    <row r="209" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D209" s="6"/>
     </row>
-    <row r="210" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D210" s="6"/>
     </row>
-    <row r="211" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D211" s="6"/>
     </row>
-    <row r="212" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D212" s="6"/>
     </row>
-    <row r="213" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D213" s="6"/>
     </row>
-    <row r="214" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D214" s="6"/>
     </row>
-    <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D215" s="6"/>
     </row>
-    <row r="216" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D216" s="6"/>
     </row>
-    <row r="217" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D217" s="6"/>
     </row>
-    <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D218" s="6"/>
     </row>
-    <row r="219" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D219" s="6"/>
     </row>
-    <row r="220" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D220" s="6"/>
     </row>
-    <row r="221" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D221" s="6"/>
     </row>
-    <row r="222" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D222" s="6"/>
     </row>
-    <row r="223" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D223" s="6"/>
     </row>
-    <row r="224" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D224" s="6"/>
     </row>
-    <row r="225" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D225" s="6"/>
     </row>
-    <row r="226" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D226" s="6"/>
     </row>
-    <row r="227" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D227" s="6"/>
     </row>
-    <row r="228" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D228" s="6"/>
     </row>
-    <row r="229" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D229" s="6"/>
     </row>
-    <row r="230" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D230" s="6"/>
     </row>
-    <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D231" s="6"/>
     </row>
-    <row r="232" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D232" s="6"/>
     </row>
-    <row r="233" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D233" s="6"/>
     </row>
-    <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D234" s="6"/>
     </row>
-    <row r="235" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D235" s="6"/>
     </row>
-    <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D236" s="6"/>
     </row>
-    <row r="237" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D237" s="6"/>
     </row>
-    <row r="238" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D238" s="6"/>
     </row>
-    <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D239" s="6"/>
     </row>
-    <row r="240" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D240" s="6"/>
     </row>
-    <row r="241" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D241" s="6"/>
     </row>
-    <row r="242" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D242" s="6"/>
     </row>
-    <row r="243" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D243" s="6"/>
     </row>
-    <row r="244" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D244" s="6"/>
     </row>
-    <row r="245" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D245" s="6"/>
     </row>
-    <row r="246" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D246" s="6"/>
     </row>
-    <row r="247" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D247" s="6"/>
     </row>
-    <row r="248" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D248" s="6"/>
     </row>
-    <row r="249" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D249" s="6"/>
     </row>
-    <row r="250" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D250" s="6"/>
     </row>
-    <row r="251" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D251" s="6"/>
     </row>
-    <row r="252" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D252" s="6"/>
     </row>
-    <row r="253" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D253" s="6"/>
     </row>
-    <row r="254" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D254" s="6"/>
     </row>
-    <row r="255" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D255" s="6"/>
     </row>
-    <row r="256" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D256" s="6"/>
     </row>
-    <row r="257" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D257" s="6"/>
     </row>
-    <row r="258" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D258" s="6"/>
     </row>
-    <row r="259" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D259" s="6"/>
     </row>
-    <row r="260" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D260" s="6"/>
     </row>
-    <row r="261" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D261" s="6"/>
     </row>
-    <row r="262" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D262" s="6"/>
     </row>
-    <row r="263" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D263" s="6"/>
     </row>
-    <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D264" s="6"/>
     </row>
-    <row r="265" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D265" s="6"/>
     </row>
-    <row r="266" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D266" s="6"/>
     </row>
-    <row r="267" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D267" s="6"/>
     </row>
-    <row r="268" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D268" s="6"/>
     </row>
-    <row r="269" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D269" s="6"/>
     </row>
-    <row r="270" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D270" s="6"/>
     </row>
-    <row r="271" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D271" s="6"/>
     </row>
-    <row r="272" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D272" s="6"/>
     </row>
-    <row r="273" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D273" s="6"/>
     </row>
-    <row r="274" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D274" s="6"/>
     </row>
-    <row r="275" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D275" s="6"/>
     </row>
-    <row r="276" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D276" s="6"/>
     </row>
-    <row r="277" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D277" s="6"/>
     </row>
-    <row r="278" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D278" s="6"/>
     </row>
-    <row r="279" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D279" s="6"/>
     </row>
-    <row r="280" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D280" s="6"/>
     </row>
-    <row r="281" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D281" s="6"/>
     </row>
-    <row r="282" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D282" s="6"/>
     </row>
-    <row r="283" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D283" s="6"/>
     </row>
-    <row r="284" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D284" s="6"/>
     </row>
-    <row r="285" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D285" s="6"/>
     </row>
-    <row r="286" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D286" s="6"/>
     </row>
-    <row r="287" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D287" s="6"/>
     </row>
-    <row r="288" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D288" s="6"/>
     </row>
-    <row r="289" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D289" s="6"/>
     </row>
-    <row r="290" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D290" s="6"/>
     </row>
-    <row r="291" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D291" s="6"/>
     </row>
-    <row r="292" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D292" s="6"/>
     </row>
-    <row r="293" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D293" s="6"/>
     </row>
-    <row r="294" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D294" s="6"/>
     </row>
-    <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D295" s="6"/>
     </row>
-    <row r="296" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D296" s="6"/>
     </row>
-    <row r="297" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D297" s="6"/>
     </row>
-    <row r="298" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D298" s="6"/>
     </row>
-    <row r="299" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D299" s="6"/>
     </row>
-    <row r="300" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D300" s="6"/>
     </row>
-    <row r="301" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D301" s="6"/>
     </row>
-    <row r="302" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D302" s="6"/>
     </row>
-    <row r="303" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D303" s="6"/>
     </row>
-    <row r="304" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D304" s="6"/>
     </row>
-    <row r="305" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D305" s="6"/>
     </row>
-    <row r="306" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D306" s="6"/>
     </row>
-    <row r="307" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D307" s="6"/>
     </row>
-    <row r="308" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D308" s="6"/>
     </row>
-    <row r="309" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D309" s="6"/>
     </row>
-    <row r="310" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D310" s="6"/>
     </row>
-    <row r="311" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D311" s="6"/>
     </row>
-    <row r="312" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D312" s="6"/>
     </row>
-    <row r="313" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D313" s="6"/>
     </row>
-    <row r="314" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D314" s="6"/>
     </row>
-    <row r="315" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D315" s="6"/>
     </row>
-    <row r="316" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D316" s="6"/>
     </row>
-    <row r="317" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D317" s="6"/>
     </row>
-    <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D318" s="6"/>
     </row>
-    <row r="319" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D319" s="6"/>
     </row>
-    <row r="320" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D320" s="6"/>
     </row>
-    <row r="321" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D321" s="6"/>
     </row>
-    <row r="322" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D322" s="6"/>
     </row>
-    <row r="323" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D323" s="6"/>
     </row>
-    <row r="324" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D324" s="6"/>
     </row>
-    <row r="325" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D325" s="6"/>
     </row>
-    <row r="326" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D326" s="6"/>
     </row>
-    <row r="327" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D327" s="6"/>
     </row>
-    <row r="328" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D328" s="6"/>
     </row>
-    <row r="329" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D329" s="6"/>
     </row>
-    <row r="330" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D330" s="6"/>
     </row>
-    <row r="331" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="331" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D331" s="6"/>
     </row>
-    <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D332" s="6"/>
     </row>
-    <row r="333" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D333" s="6"/>
     </row>
-    <row r="334" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D334" s="6"/>
     </row>
-    <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D335" s="6"/>
     </row>
-    <row r="336" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D336" s="6"/>
     </row>
-    <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D337" s="6"/>
     </row>
-    <row r="338" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D338" s="6"/>
     </row>
-    <row r="339" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D339" s="6"/>
     </row>
-    <row r="340" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D340" s="6"/>
     </row>
-    <row r="341" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D341" s="6"/>
     </row>
-    <row r="342" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D342" s="6"/>
     </row>
-    <row r="343" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D343" s="6"/>
     </row>
-    <row r="344" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D344" s="6"/>
     </row>
-    <row r="345" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D345" s="6"/>
     </row>
-    <row r="346" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D346" s="6"/>
     </row>
-    <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D347" s="6"/>
     </row>
-    <row r="348" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D348" s="6"/>
     </row>
-    <row r="349" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D349" s="6"/>
     </row>
-    <row r="350" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D350" s="6"/>
     </row>
-    <row r="351" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D351" s="6"/>
     </row>
-    <row r="352" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D352" s="6"/>
     </row>
-    <row r="353" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D353" s="6"/>
     </row>
-    <row r="354" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D354" s="6"/>
     </row>
-    <row r="355" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D355" s="6"/>
     </row>
-    <row r="356" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D356" s="6"/>
     </row>
-    <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D357" s="6"/>
     </row>
-    <row r="358" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D358" s="6"/>
     </row>
-    <row r="359" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D359" s="6"/>
     </row>
-    <row r="360" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D360" s="6"/>
     </row>
-    <row r="361" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D361" s="6"/>
     </row>
-    <row r="362" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D362" s="6"/>
     </row>
-    <row r="363" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D363" s="6"/>
     </row>
-    <row r="364" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D364" s="6"/>
     </row>
-    <row r="365" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D365" s="6"/>
     </row>
-    <row r="366" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D366" s="6"/>
     </row>
-    <row r="367" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D367" s="6"/>
     </row>
-    <row r="368" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D368" s="6"/>
     </row>
-    <row r="369" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D369" s="6"/>
     </row>
-    <row r="370" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D370" s="6"/>
     </row>
-    <row r="371" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D371" s="6"/>
     </row>
-    <row r="372" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D372" s="6"/>
     </row>
-    <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D373" s="6"/>
     </row>
-    <row r="374" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D374" s="6"/>
     </row>
-    <row r="375" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D375" s="6"/>
     </row>
-    <row r="376" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D376" s="6"/>
     </row>
-    <row r="377" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D377" s="6"/>
     </row>
-    <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D378" s="6"/>
     </row>
-    <row r="379" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D379" s="6"/>
     </row>
-    <row r="380" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D380" s="6"/>
     </row>
-    <row r="381" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D381" s="6"/>
     </row>
-    <row r="382" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D382" s="6"/>
     </row>
-    <row r="383" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D383" s="6"/>
     </row>
-    <row r="384" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D384" s="6"/>
     </row>
-    <row r="385" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D385" s="6"/>
     </row>
-    <row r="386" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D386" s="6"/>
     </row>
-    <row r="387" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D387" s="6"/>
     </row>
-    <row r="388" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D388" s="6"/>
     </row>
-    <row r="389" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D389" s="6"/>
     </row>
-    <row r="390" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D390" s="6"/>
     </row>
-    <row r="391" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D391" s="6"/>
     </row>
-    <row r="392" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D392" s="6"/>
     </row>
-    <row r="393" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D393" s="6"/>
     </row>
-    <row r="394" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D394" s="6"/>
     </row>
-    <row r="395" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D395" s="6"/>
     </row>
-    <row r="396" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D396" s="6"/>
     </row>
-    <row r="397" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D397" s="6"/>
     </row>
-    <row r="398" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D398" s="6"/>
     </row>
-    <row r="399" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D399" s="6"/>
     </row>
-    <row r="400" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D400" s="6"/>
     </row>
-    <row r="401" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D401" s="6"/>
     </row>
-    <row r="402" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D402" s="6"/>
     </row>
-    <row r="403" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D403" s="6"/>
     </row>
-    <row r="404" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D404" s="6"/>
     </row>
-    <row r="405" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D405" s="6"/>
     </row>
-    <row r="406" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D406" s="6"/>
     </row>
-    <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D407" s="6"/>
     </row>
-    <row r="408" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D408" s="6"/>
     </row>
-    <row r="409" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D409" s="6"/>
     </row>
-    <row r="410" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D410" s="6"/>
     </row>
-    <row r="411" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D411" s="6"/>
     </row>
-    <row r="412" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D412" s="6"/>
     </row>
-    <row r="413" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D413" s="6"/>
     </row>
-    <row r="414" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D414" s="6"/>
     </row>
-    <row r="415" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D415" s="6"/>
     </row>
-    <row r="416" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D416" s="6"/>
     </row>
-    <row r="417" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D417" s="6"/>
     </row>
-    <row r="418" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D418" s="6"/>
     </row>
-    <row r="419" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D419" s="6"/>
     </row>
-    <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D420" s="6"/>
     </row>
-    <row r="421" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D421" s="6"/>
     </row>
-    <row r="422" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D422" s="6"/>
     </row>
-    <row r="423" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D423" s="6"/>
     </row>
-    <row r="424" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D424" s="6"/>
     </row>
-    <row r="425" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D425" s="6"/>
     </row>
-    <row r="426" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D426" s="6"/>
     </row>
-    <row r="427" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D427" s="6"/>
     </row>
-    <row r="428" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D428" s="6"/>
     </row>
-    <row r="429" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D429" s="6"/>
     </row>
-    <row r="430" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D430" s="6"/>
     </row>
-    <row r="431" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D431" s="6"/>
     </row>
-    <row r="432" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D432" s="6"/>
     </row>
-    <row r="433" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D433" s="6"/>
     </row>
-    <row r="434" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D434" s="6"/>
     </row>
-    <row r="435" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D435" s="6"/>
     </row>
-    <row r="436" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D436" s="6"/>
     </row>
-    <row r="437" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D437" s="6"/>
     </row>
-    <row r="438" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D438" s="6"/>
     </row>
-    <row r="439" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D439" s="6"/>
     </row>
-    <row r="440" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D440" s="6"/>
     </row>
-    <row r="441" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D441" s="6"/>
     </row>
-    <row r="442" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D442" s="6"/>
     </row>
-    <row r="443" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D443" s="6"/>
     </row>
-    <row r="444" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D444" s="6"/>
     </row>
-    <row r="445" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D445" s="6"/>
     </row>
-    <row r="446" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D446" s="6"/>
     </row>
-    <row r="447" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D447" s="6"/>
     </row>
-    <row r="448" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D448" s="6"/>
     </row>
-    <row r="449" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D449" s="6"/>
     </row>
-    <row r="450" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D450" s="6"/>
     </row>
-    <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D451" s="6"/>
     </row>
-    <row r="452" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D452" s="6"/>
     </row>
-    <row r="453" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D453" s="6"/>
     </row>
-    <row r="454" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D454" s="6"/>
     </row>
-    <row r="455" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D455" s="6"/>
     </row>
-    <row r="456" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D456" s="6"/>
     </row>
-    <row r="457" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D457" s="6"/>
     </row>
-    <row r="458" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D458" s="6"/>
     </row>
-    <row r="459" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D459" s="6"/>
     </row>
-    <row r="460" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="460" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D460" s="6"/>
     </row>
-    <row r="461" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D461" s="6"/>
     </row>
-    <row r="462" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D462" s="6"/>
     </row>
-    <row r="463" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D463" s="6"/>
     </row>
-    <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D464" s="6"/>
     </row>
-    <row r="465" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D465" s="6"/>
     </row>
-    <row r="466" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D466" s="6"/>
     </row>
-    <row r="467" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D467" s="6"/>
     </row>
-    <row r="468" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D468" s="6"/>
     </row>
-    <row r="469" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D469" s="6"/>
     </row>
-    <row r="470" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D470" s="6"/>
     </row>
-    <row r="471" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D471" s="6"/>
     </row>
-    <row r="472" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D472" s="6"/>
     </row>
-    <row r="473" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D473" s="6"/>
     </row>
-    <row r="474" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D474" s="6"/>
     </row>
-    <row r="475" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D475" s="6"/>
     </row>
-    <row r="476" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D476" s="6"/>
     </row>
-    <row r="477" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D477" s="6"/>
     </row>
-    <row r="478" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D478" s="6"/>
     </row>
-    <row r="479" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D479" s="6"/>
     </row>
-    <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D480" s="6"/>
     </row>
-    <row r="481" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D481" s="6"/>
     </row>
-    <row r="482" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D482" s="6"/>
     </row>
-    <row r="483" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D483" s="6"/>
     </row>
-    <row r="484" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D484" s="6"/>
     </row>
-    <row r="485" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D485" s="6"/>
     </row>
-    <row r="486" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D486" s="6"/>
     </row>
-    <row r="487" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D487" s="6"/>
     </row>
-    <row r="488" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="488" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D488" s="6"/>
     </row>
-    <row r="489" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D489" s="6"/>
     </row>
-    <row r="490" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D490" s="6"/>
     </row>
-    <row r="491" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D491" s="6"/>
     </row>
-    <row r="492" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D492" s="6"/>
     </row>
-    <row r="493" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D493" s="6"/>
     </row>
-    <row r="494" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="494" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D494" s="6"/>
     </row>
-    <row r="495" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D495" s="6"/>
     </row>
-    <row r="496" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D496" s="6"/>
     </row>
-    <row r="497" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D497" s="6"/>
     </row>
-    <row r="498" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D498" s="6"/>
     </row>
-    <row r="499" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D499" s="6"/>
     </row>
-    <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D500" s="6"/>
     </row>
-    <row r="501" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D501" s="6"/>
     </row>
-    <row r="502" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="502" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D502" s="6"/>
     </row>
-    <row r="503" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D503" s="6"/>
     </row>
-    <row r="504" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="504" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D504" s="6"/>
     </row>
-    <row r="505" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D505" s="6"/>
     </row>
-    <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D506" s="6"/>
     </row>
-    <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D507" s="6"/>
     </row>
-    <row r="508" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="508" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D508" s="6"/>
     </row>
-    <row r="509" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="509" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D509" s="6"/>
     </row>
-    <row r="510" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="510" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D510" s="6"/>
     </row>
-    <row r="511" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="511" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D511" s="6"/>
     </row>
-    <row r="512" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="512" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D512" s="6"/>
     </row>
-    <row r="513" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D513" s="6"/>
     </row>
-    <row r="514" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D514" s="6"/>
     </row>
-    <row r="515" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="515" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D515" s="6"/>
     </row>
   </sheetData>
